--- a/Documentation/Database_Design/Database_Dictionary.xlsx
+++ b/Documentation/Database_Design/Database_Dictionary.xlsx
@@ -4,14 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="8280" tabRatio="776" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="1. Table Overview" sheetId="1" r:id="rId1"/>
     <sheet name="2. Data Lineage Selection" sheetId="2" r:id="rId2"/>
+    <sheet name="3. Executing_plan" sheetId="3" r:id="rId3"/>
+    <sheet name="3.1. API_DB_8" sheetId="4" r:id="rId4"/>
+    <sheet name="3.2. API_DB_7" sheetId="5" r:id="rId5"/>
+    <sheet name="3.3. API_DB_1" sheetId="6" r:id="rId6"/>
+    <sheet name="3.4. API_DB_2" sheetId="7" r:id="rId7"/>
+    <sheet name="3.5. API_DB_3" sheetId="8" r:id="rId8"/>
+    <sheet name="3.6. API_DB_4" sheetId="9" r:id="rId9"/>
+    <sheet name="3.7. API_DB_5" sheetId="10" r:id="rId10"/>
+    <sheet name="3.8. API_DB_6" sheetId="11" r:id="rId11"/>
+    <sheet name="3.9. API_DB_15" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Data Lineage Selection'!$A$2:$LY$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Executing_plan'!$A$2:$LW$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="205">
   <si>
     <t>No</t>
   </si>
@@ -781,6 +792,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>1.</t>
     </r>
     <r>
@@ -1044,6 +1062,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1179,6 +1204,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>order_id</t>
     </r>
     <r>
@@ -1255,6 +1288,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1451,6 +1491,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1605,6 +1652,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>product_name</t>
     </r>
     <r>
@@ -1741,6 +1796,107 @@
   </si>
   <si>
     <t xml:space="preserve">        WHERE i.order_id = '2'</t>
+  </si>
+  <si>
+    <t>Query</t>
+  </si>
+  <si>
+    <t>Executing plan</t>
+  </si>
+  <si>
+    <t>SELECT 
+          inven.quantity_storage 
+        FROM inventory inven
+        JOIN products prod
+          ON inven.product_id = prod.product_id
+        WHERE product_name = '3 Day WKND';</t>
+  </si>
+  <si>
+    <t>SELECT 
+          first_name, 
+          last_name, 
+          customer_id 
+        FROM customers 
+        WHERE username = 'nguyentrungtin2001@gmail.com' AND password = '09004092001'</t>
+  </si>
+  <si>
+    <t>SELECT 
+          customer_id, 
+          first_name, 
+          last_name, 
+          email, 
+          address 
+        FROM customers;</t>
+  </si>
+  <si>
+    <t>SELECT 
+            procduct.product_name, 
+            sbi.quantity, 
+            procduct.price_unit, 
+            procduct.product_image 
+          FROM personal_shopping_bag AS psb 
+          JOIN customers AS c 
+            ON psb.customer_id = c.customer_id 
+          JOIN shopping_bag_item AS sbi
+            ON psb.shopping_bag_id = sbi.shopping_bag_id 
+          JOIN products AS procduct
+            ON procduct.product_id = sbi.product_id 
+          WHERE c.customer_id = '1';</t>
+  </si>
+  <si>
+    <t>SELECT 
+          inven.inventory_id, 
+          product_table.product_name, 
+          inven.quantity_storage, 
+          w.name, 
+          w.location 
+        FROM inventory inven
+        JOIN ware_houses w 
+          ON inven.warehouse_id = w.warehouse_id
+        JOIN products product_table
+          ON inven.product_id = product_table.product_id;</t>
+  </si>
+  <si>
+    <t>SELECT * FROM ware_houses;</t>
+  </si>
+  <si>
+    <t>SELECT 
+          o.order_id, 
+          o.order_date, 
+          o.total_amount,
+          o.status_order, 
+          CONCAT(c.first_name, ' ', c.last_name) AS name, 
+          o.customer_id 
+        FROM orders o 
+        JOIN customers c 
+          ON o.customer_id = c.customer_id;</t>
+  </si>
+  <si>
+    <t>SELECT 
+           od_detail.order_id,
+            od_detail.order_detail_id,
+           pymt.payment_id,
+            od_detail.quantity,
+            pymt.method,
+            pymt.status_payment,
+            pymt.payment_gateway_id,
+            inven.product_id,
+            product_table.product_name,
+            product_table.price_unit,
+            product_table.product_category
+        FROM order_details od_detail
+        JOIN payments pymt 
+            ON od_detail.order_id = pymt.order_id
+        JOIN order_details_inventory od_detail_inven
+            ON od_detail.order_detail_id = od_detail_inven.order_detail_id
+        JOIN inventory inven
+            ON od_detail_inven.inventory_id = inven.inventory_id
+       JOIN products product_table
+            ON inven.product_id = product_table.product_id
+        WHERE od_detail.order_id = '5';</t>
+  </si>
+  <si>
+    <t>SELECT * FROM coupons;</t>
   </si>
 </sst>
 </file>
@@ -1772,7 +1928,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1780,7 +1936,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1941,6 +2097,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1954,12 +2116,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2328,10 +2484,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -2458,7 +2614,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2475,13 +2631,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2492,7 +2642,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2507,10 +2657,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2522,7 +2678,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2531,7 +2687,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2540,20 +2696,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2567,34 +2750,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -4770,6 +4938,513 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>381635</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="635"/>
+          <a:ext cx="3429000" cy="1285875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>536575</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>23495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="635"/>
+          <a:ext cx="9070340" cy="4594860"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>162560</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>13970</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="635"/>
+          <a:ext cx="5648325" cy="2390775"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>276860</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>99695</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="635"/>
+          <a:ext cx="4543425" cy="2476500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>499745</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>184785</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>43815</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5376545" y="635"/>
+          <a:ext cx="5171440" cy="4615180"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>488315</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>126365</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>375285</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>73025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5365115" y="4515485"/>
+          <a:ext cx="5373370" cy="3238500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30480" y="635"/>
+          <a:ext cx="3352800" cy="1343025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>324485</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="635"/>
+          <a:ext cx="3371850" cy="1304925"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7620" y="7620"/>
+          <a:ext cx="8653780" cy="4331970"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>153035</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="15240"/>
+          <a:ext cx="6858000" cy="3448050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>635</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>635</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>162560</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>74930</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="635" y="635"/>
+          <a:ext cx="3209925" cy="1171575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5032,195 +5707,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="B2:E14"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="4.11111111111111" style="2" customWidth="1"/>
-    <col min="3" max="3" width="22.1111111111111" style="43" customWidth="1"/>
-    <col min="4" max="4" width="28.2222222222222" style="43" customWidth="1"/>
-    <col min="5" max="5" width="44.1111111111111" style="43" customWidth="1"/>
+    <col min="3" max="3" width="22.1111111111111" style="47" customWidth="1"/>
+    <col min="4" max="4" width="28.2222222222222" style="47" customWidth="1"/>
+    <col min="5" max="5" width="44.1111111111111" style="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" s="7" customFormat="1" spans="2:5">
-      <c r="B2" s="41" t="s">
+    <row r="2" s="4" customFormat="1" spans="2:5">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" s="7" customFormat="1" spans="2:5">
-      <c r="B3" s="39">
+    <row r="3" s="4" customFormat="1" spans="2:5">
+      <c r="B3" s="32">
         <v>1</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="33" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" s="7" customFormat="1" spans="2:5">
-      <c r="B4" s="31">
+    <row r="4" s="4" customFormat="1" spans="2:5">
+      <c r="B4" s="42">
         <v>2</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="48" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" s="7" customFormat="1" spans="2:5">
-      <c r="B5" s="39">
+    <row r="5" s="4" customFormat="1" spans="2:5">
+      <c r="B5" s="32">
         <v>3</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="40" t="s">
+      <c r="D5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="33" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" s="7" customFormat="1" spans="2:5">
-      <c r="B6" s="39">
+    <row r="6" s="4" customFormat="1" spans="2:5">
+      <c r="B6" s="32">
         <v>4</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="33" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" s="7" customFormat="1" spans="2:5">
-      <c r="B7" s="39">
+    <row r="7" s="4" customFormat="1" spans="2:5">
+      <c r="B7" s="32">
         <v>5</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="C7" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="33" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" s="7" customFormat="1" spans="2:5">
-      <c r="B8" s="39">
+    <row r="8" s="4" customFormat="1" spans="2:5">
+      <c r="B8" s="32">
         <v>6</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="C8" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="E8" s="33" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" s="7" customFormat="1" spans="2:5">
-      <c r="B9" s="31">
+    <row r="9" s="4" customFormat="1" spans="2:5">
+      <c r="B9" s="42">
         <v>7</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="48" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" s="7" customFormat="1" spans="2:5">
-      <c r="B10" s="31">
+    <row r="10" s="4" customFormat="1" spans="2:5">
+      <c r="B10" s="42">
         <v>8</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="48" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" s="7" customFormat="1" spans="2:5">
-      <c r="B11" s="39">
+    <row r="11" s="4" customFormat="1" spans="2:5">
+      <c r="B11" s="32">
         <v>9</v>
       </c>
-      <c r="C11" s="40" t="s">
+      <c r="C11" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D11" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E11" s="33" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" s="7" customFormat="1" spans="2:5">
-      <c r="B12" s="39">
+    <row r="12" s="4" customFormat="1" spans="2:5">
+      <c r="B12" s="32">
         <v>10</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="D12" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="33" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" s="7" customFormat="1" spans="2:5">
-      <c r="B13" s="39">
+    <row r="13" s="4" customFormat="1" spans="2:5">
+      <c r="B13" s="32">
         <v>11</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="31" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="31">
+      <c r="B14" s="42">
         <v>12</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="49" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="49" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5231,163 +5908,207 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:LY49"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.7777777777778" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.8888888888889" style="5" customWidth="1"/>
-    <col min="3" max="3" width="40.7777777777778" style="6" customWidth="1"/>
-    <col min="4" max="4" width="50.7777777777778" style="6" customWidth="1"/>
-    <col min="5" max="5" width="38.6388888888889" style="7" customWidth="1"/>
-    <col min="6" max="6" width="50.7777777777778" style="6" customWidth="1"/>
-    <col min="7" max="7" width="22.6111111111111" style="7" customWidth="1"/>
-    <col min="8" max="8" width="51.5555555555556" style="6" customWidth="1"/>
-    <col min="9" max="11" width="50.7777777777778" style="6" customWidth="1"/>
-    <col min="12" max="12" width="8.88888888888889" style="7"/>
+    <col min="2" max="2" width="11.8888888888889" style="2" customWidth="1"/>
+    <col min="3" max="3" width="40.7777777777778" style="5" customWidth="1"/>
+    <col min="4" max="4" width="50.7777777777778" style="5" customWidth="1"/>
+    <col min="5" max="5" width="38.6388888888889" style="4" customWidth="1"/>
+    <col min="6" max="6" width="50.7777777777778" style="5" customWidth="1"/>
+    <col min="7" max="7" width="22.6111111111111" style="4" customWidth="1"/>
+    <col min="8" max="8" width="51.5555555555556" style="5" customWidth="1"/>
+    <col min="9" max="11" width="50.7777777777778" style="5" customWidth="1"/>
+    <col min="12" max="12" width="8.88888888888889" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="7"/>
+      <c r="A1" s="4"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="7"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="41"/>
+      <c r="L2" s="34"/>
     </row>
-    <row r="3" s="3" customFormat="1" ht="28.8" hidden="1" spans="1:12">
-      <c r="A3" s="11" t="s">
+    <row r="3" s="3" customFormat="1" ht="28.8" spans="1:12">
+      <c r="A3" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="46" t="s">
+      <c r="K3" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="42"/>
+      <c r="L3" s="35"/>
     </row>
-    <row r="4" s="2" customFormat="1" ht="43.2" hidden="1" spans="1:12">
-      <c r="A4" s="11" t="s">
+    <row r="4" s="2" customFormat="1" ht="43.2" spans="1:12">
+      <c r="A4" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="11" t="s">
         <v>66</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="L4" s="38"/>
+      <c r="L4" s="31"/>
     </row>
-    <row r="5" s="2" customFormat="1" ht="72" hidden="1" spans="1:337">
-      <c r="A5" s="11" t="s">
+    <row r="5" s="2" customFormat="1" ht="72" spans="1:337">
+      <c r="A5" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="11" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="16" t="s">
@@ -5396,16 +6117,16 @@
       <c r="H5" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="L5" s="42"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -5732,8 +6453,8 @@
       <c r="LX5" s="3"/>
       <c r="LY5" s="3"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="30" hidden="1" customHeight="1" spans="1:337">
-      <c r="A6" s="17" t="s">
+    <row r="6" s="2" customFormat="1" ht="30" customHeight="1" spans="1:337">
+      <c r="A6" s="37" t="s">
         <v>79</v>
       </c>
       <c r="B6" s="18" t="s">
@@ -5763,10 +6484,10 @@
       <c r="J6" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="42"/>
+      <c r="L6" s="35"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -6093,8 +6814,8 @@
       <c r="LX6" s="3"/>
       <c r="LY6" s="3"/>
     </row>
-    <row r="7" s="2" customFormat="1" ht="30" hidden="1" customHeight="1" spans="1:337">
-      <c r="A7" s="21"/>
+    <row r="7" s="2" customFormat="1" ht="30" customHeight="1" spans="1:337">
+      <c r="A7" s="38"/>
       <c r="B7" s="22"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -6104,10 +6825,10 @@
       <c r="H7" s="23"/>
       <c r="I7" s="26"/>
       <c r="J7" s="26"/>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="L7" s="42"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -6434,8 +7155,8 @@
       <c r="LX7" s="3"/>
       <c r="LY7" s="3"/>
     </row>
-    <row r="8" s="2" customFormat="1" ht="30" hidden="1" customHeight="1" spans="1:337">
-      <c r="A8" s="24"/>
+    <row r="8" s="2" customFormat="1" ht="30" customHeight="1" spans="1:337">
+      <c r="A8" s="39"/>
       <c r="B8" s="25"/>
       <c r="C8" s="26"/>
       <c r="D8" s="26"/>
@@ -6443,16 +7164,16 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
       <c r="H8" s="26"/>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="L8" s="42"/>
+      <c r="L8" s="35"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -6779,59 +7500,59 @@
       <c r="LX8" s="3"/>
       <c r="LY8" s="3"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="72" hidden="1" spans="1:12">
-      <c r="A9" s="27" t="s">
+    <row r="9" s="1" customFormat="1" ht="72" spans="1:12">
+      <c r="A9" s="40" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="L9" s="38"/>
+      <c r="L9" s="31"/>
     </row>
-    <row r="10" s="1" customFormat="1" hidden="1" spans="1:12">
-      <c r="A10" s="27" t="s">
+    <row r="10" s="1" customFormat="1" spans="1:12">
+      <c r="A10" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="13" t="s">
         <v>75</v>
       </c>
       <c r="G10" s="16" t="s">
@@ -6840,106 +7561,106 @@
       <c r="H10" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K10" s="15" t="s">
+      <c r="K10" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="L10" s="38"/>
+      <c r="L10" s="31"/>
     </row>
-    <row r="11" s="1" customFormat="1" ht="100.8" hidden="1" spans="1:12">
-      <c r="A11" s="27" t="s">
+    <row r="11" s="1" customFormat="1" ht="100.8" spans="1:12">
+      <c r="A11" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="L11" s="38"/>
+      <c r="L11" s="31"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="158.4" hidden="1" spans="1:12">
-      <c r="A12" s="27" t="s">
+    <row r="12" s="1" customFormat="1" ht="158.4" spans="1:12">
+      <c r="A12" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="15" t="s">
+      <c r="K12" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="L12" s="38"/>
+      <c r="L12" s="31"/>
     </row>
-    <row r="13" s="1" customFormat="1" hidden="1" spans="1:12">
-      <c r="A13" s="27" t="s">
+    <row r="13" s="1" customFormat="1" spans="1:12">
+      <c r="A13" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="13" t="s">
         <v>75</v>
       </c>
       <c r="G13" s="16" t="s">
@@ -6948,70 +7669,70 @@
       <c r="H13" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="L13" s="38"/>
+      <c r="L13" s="31"/>
     </row>
-    <row r="14" s="1" customFormat="1" ht="72" hidden="1" spans="1:12">
-      <c r="A14" s="30" t="s">
+    <row r="14" s="1" customFormat="1" ht="72" spans="1:12">
+      <c r="A14" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="13" t="s">
         <v>124</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="13" t="s">
         <v>125</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="15" t="s">
+      <c r="K14" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="L14" s="38"/>
+      <c r="L14" s="31"/>
     </row>
-    <row r="15" s="1" customFormat="1" hidden="1" spans="1:12">
-      <c r="A15" s="30" t="s">
+    <row r="15" s="1" customFormat="1" spans="1:12">
+      <c r="A15" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="13" t="s">
         <v>75</v>
       </c>
       <c r="G15" s="16" t="s">
@@ -7020,391 +7741,383 @@
       <c r="H15" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K15" s="15" t="s">
+      <c r="K15" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="L15" s="38"/>
+      <c r="L15" s="31"/>
     </row>
-    <row r="16" s="1" customFormat="1" hidden="1" spans="1:12">
-      <c r="A16" s="30" t="s">
+    <row r="16" s="1" customFormat="1" spans="1:12">
+      <c r="A16" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H16" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="L16" s="38"/>
+      <c r="L16" s="31"/>
     </row>
-    <row r="17" s="1" customFormat="1" ht="120" hidden="1" customHeight="1" spans="1:12">
-      <c r="A17" s="32" t="s">
+    <row r="17" s="1" customFormat="1" ht="120" customHeight="1" spans="1:12">
+      <c r="A17" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="K17" s="15" t="s">
+      <c r="K17" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="L17" s="38"/>
+      <c r="L17" s="31"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="60" customHeight="1" spans="1:12">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="13" t="s">
         <v>148</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="K18" s="15" t="s">
+      <c r="K18" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="L18" s="38"/>
+      <c r="L18" s="31"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="120" customHeight="1" spans="1:12">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="43" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="15" t="s">
+      <c r="K19" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="L19" s="38"/>
+      <c r="L19" s="31"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="120" customHeight="1" spans="1:12">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="G20" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="15" t="s">
+      <c r="H20" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="15" t="s">
+      <c r="K20" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="L20" s="38"/>
+      <c r="L20" s="31"/>
     </row>
-    <row r="21" s="1" customFormat="1" ht="120" hidden="1" customHeight="1" spans="1:12">
-      <c r="A21" s="32" t="s">
+    <row r="21" s="1" customFormat="1" ht="120" customHeight="1" spans="1:12">
+      <c r="A21" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="15" t="s">
+      <c r="G21" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="H21" s="15" t="s">
+      <c r="H21" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="15" t="s">
+      <c r="K21" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="L21" s="38"/>
+      <c r="L21" s="31"/>
     </row>
-    <row r="22" s="1" customFormat="1" ht="55" hidden="1" customHeight="1" spans="1:12">
-      <c r="A22" s="34" t="s">
+    <row r="22" s="1" customFormat="1" ht="55" customHeight="1" spans="1:12">
+      <c r="A22" s="45" t="s">
         <v>169</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="13" t="s">
         <v>172</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F22" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="H22" s="15" t="s">
+      <c r="H22" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="K22" s="15" t="s">
+      <c r="K22" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="L22" s="38"/>
+      <c r="L22" s="31"/>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:12">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="38"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="31"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:12">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="38"/>
+      <c r="A24" s="31"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="31"/>
     </row>
     <row r="32" spans="3:3">
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="34" spans="3:3">
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="35" spans="3:3">
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="36" spans="3:3">
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="37" spans="3:3">
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="38" spans="3:3">
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="39" spans="3:3">
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="5" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="40" spans="3:3">
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="5" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="41" spans="3:3">
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="5" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="42" spans="3:3">
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="5" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="43" spans="3:3">
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="5" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="44" spans="3:3">
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="5" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="45" spans="3:3">
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="5" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="46" spans="3:3">
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="5" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="47" spans="3:3">
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="5" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="48" spans="3:3">
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="5" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="49" spans="3:3">
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="5" t="s">
         <v>193</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:LY22" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="PAYMENT_HANDLING_Specific_Handling_URL"/>
-      </filters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <mergeCells count="10">
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:B8"/>
@@ -7420,4 +8133,1777 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:LW15"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.7777777777778" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.8888888888889" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.7777777777778" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.6388888888889" style="4" customWidth="1"/>
+    <col min="5" max="5" width="50.7777777777778" style="5" customWidth="1"/>
+    <col min="6" max="6" width="22.6111111111111" style="4" customWidth="1"/>
+    <col min="7" max="8" width="51.5555555555556" style="5" customWidth="1"/>
+    <col min="9" max="9" width="50.7777777777778" style="5" customWidth="1"/>
+    <col min="10" max="10" width="8.88888888888889" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:10">
+      <c r="A1" s="4"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:10">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="J2" s="34"/>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="86.4" spans="1:10">
+      <c r="A3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="35"/>
+    </row>
+    <row r="4" s="2" customFormat="1" ht="100.8" spans="1:10">
+      <c r="A4" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="100.8" spans="1:335">
+      <c r="A5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="3"/>
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="3"/>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3"/>
+      <c r="AL5" s="3"/>
+      <c r="AM5" s="3"/>
+      <c r="AN5" s="3"/>
+      <c r="AO5" s="3"/>
+      <c r="AP5" s="3"/>
+      <c r="AQ5" s="3"/>
+      <c r="AR5" s="3"/>
+      <c r="AS5" s="3"/>
+      <c r="AT5" s="3"/>
+      <c r="AU5" s="3"/>
+      <c r="AV5" s="3"/>
+      <c r="AW5" s="3"/>
+      <c r="AX5" s="3"/>
+      <c r="AY5" s="3"/>
+      <c r="AZ5" s="3"/>
+      <c r="BA5" s="3"/>
+      <c r="BB5" s="3"/>
+      <c r="BC5" s="3"/>
+      <c r="BD5" s="3"/>
+      <c r="BE5" s="3"/>
+      <c r="BF5" s="3"/>
+      <c r="BG5" s="3"/>
+      <c r="BH5" s="3"/>
+      <c r="BI5" s="3"/>
+      <c r="BJ5" s="3"/>
+      <c r="BK5" s="3"/>
+      <c r="BL5" s="3"/>
+      <c r="BM5" s="3"/>
+      <c r="BN5" s="3"/>
+      <c r="BO5" s="3"/>
+      <c r="BP5" s="3"/>
+      <c r="BQ5" s="3"/>
+      <c r="BR5" s="3"/>
+      <c r="BS5" s="3"/>
+      <c r="BT5" s="3"/>
+      <c r="BU5" s="3"/>
+      <c r="BV5" s="3"/>
+      <c r="BW5" s="3"/>
+      <c r="BX5" s="3"/>
+      <c r="BY5" s="3"/>
+      <c r="BZ5" s="3"/>
+      <c r="CA5" s="3"/>
+      <c r="CB5" s="3"/>
+      <c r="CC5" s="3"/>
+      <c r="CD5" s="3"/>
+      <c r="CE5" s="3"/>
+      <c r="CF5" s="3"/>
+      <c r="CG5" s="3"/>
+      <c r="CH5" s="3"/>
+      <c r="CI5" s="3"/>
+      <c r="CJ5" s="3"/>
+      <c r="CK5" s="3"/>
+      <c r="CL5" s="3"/>
+      <c r="CM5" s="3"/>
+      <c r="CN5" s="3"/>
+      <c r="CO5" s="3"/>
+      <c r="CP5" s="3"/>
+      <c r="CQ5" s="3"/>
+      <c r="CR5" s="3"/>
+      <c r="CS5" s="3"/>
+      <c r="CT5" s="3"/>
+      <c r="CU5" s="3"/>
+      <c r="CV5" s="3"/>
+      <c r="CW5" s="3"/>
+      <c r="CX5" s="3"/>
+      <c r="CY5" s="3"/>
+      <c r="CZ5" s="3"/>
+      <c r="DA5" s="3"/>
+      <c r="DB5" s="3"/>
+      <c r="DC5" s="3"/>
+      <c r="DD5" s="3"/>
+      <c r="DE5" s="3"/>
+      <c r="DF5" s="3"/>
+      <c r="DG5" s="3"/>
+      <c r="DH5" s="3"/>
+      <c r="DI5" s="3"/>
+      <c r="DJ5" s="3"/>
+      <c r="DK5" s="3"/>
+      <c r="DL5" s="3"/>
+      <c r="DM5" s="3"/>
+      <c r="DN5" s="3"/>
+      <c r="DO5" s="3"/>
+      <c r="DP5" s="3"/>
+      <c r="DQ5" s="3"/>
+      <c r="DR5" s="3"/>
+      <c r="DS5" s="3"/>
+      <c r="DT5" s="3"/>
+      <c r="DU5" s="3"/>
+      <c r="DV5" s="3"/>
+      <c r="DW5" s="3"/>
+      <c r="DX5" s="3"/>
+      <c r="DY5" s="3"/>
+      <c r="DZ5" s="3"/>
+      <c r="EA5" s="3"/>
+      <c r="EB5" s="3"/>
+      <c r="EC5" s="3"/>
+      <c r="ED5" s="3"/>
+      <c r="EE5" s="3"/>
+      <c r="EF5" s="3"/>
+      <c r="EG5" s="3"/>
+      <c r="EH5" s="3"/>
+      <c r="EI5" s="3"/>
+      <c r="EJ5" s="3"/>
+      <c r="EK5" s="3"/>
+      <c r="EL5" s="3"/>
+      <c r="EM5" s="3"/>
+      <c r="EN5" s="3"/>
+      <c r="EO5" s="3"/>
+      <c r="EP5" s="3"/>
+      <c r="EQ5" s="3"/>
+      <c r="ER5" s="3"/>
+      <c r="ES5" s="3"/>
+      <c r="ET5" s="3"/>
+      <c r="EU5" s="3"/>
+      <c r="EV5" s="3"/>
+      <c r="EW5" s="3"/>
+      <c r="EX5" s="3"/>
+      <c r="EY5" s="3"/>
+      <c r="EZ5" s="3"/>
+      <c r="FA5" s="3"/>
+      <c r="FB5" s="3"/>
+      <c r="FC5" s="3"/>
+      <c r="FD5" s="3"/>
+      <c r="FE5" s="3"/>
+      <c r="FF5" s="3"/>
+      <c r="FG5" s="3"/>
+      <c r="FH5" s="3"/>
+      <c r="FI5" s="3"/>
+      <c r="FJ5" s="3"/>
+      <c r="FK5" s="3"/>
+      <c r="FL5" s="3"/>
+      <c r="FM5" s="3"/>
+      <c r="FN5" s="3"/>
+      <c r="FO5" s="3"/>
+      <c r="FP5" s="3"/>
+      <c r="FQ5" s="3"/>
+      <c r="FR5" s="3"/>
+      <c r="FS5" s="3"/>
+      <c r="FT5" s="3"/>
+      <c r="FU5" s="3"/>
+      <c r="FV5" s="3"/>
+      <c r="FW5" s="3"/>
+      <c r="FX5" s="3"/>
+      <c r="FY5" s="3"/>
+      <c r="FZ5" s="3"/>
+      <c r="GA5" s="3"/>
+      <c r="GB5" s="3"/>
+      <c r="GC5" s="3"/>
+      <c r="GD5" s="3"/>
+      <c r="GE5" s="3"/>
+      <c r="GF5" s="3"/>
+      <c r="GG5" s="3"/>
+      <c r="GH5" s="3"/>
+      <c r="GI5" s="3"/>
+      <c r="GJ5" s="3"/>
+      <c r="GK5" s="3"/>
+      <c r="GL5" s="3"/>
+      <c r="GM5" s="3"/>
+      <c r="GN5" s="3"/>
+      <c r="GO5" s="3"/>
+      <c r="GP5" s="3"/>
+      <c r="GQ5" s="3"/>
+      <c r="GR5" s="3"/>
+      <c r="GS5" s="3"/>
+      <c r="GT5" s="3"/>
+      <c r="GU5" s="3"/>
+      <c r="GV5" s="3"/>
+      <c r="GW5" s="3"/>
+      <c r="GX5" s="3"/>
+      <c r="GY5" s="3"/>
+      <c r="GZ5" s="3"/>
+      <c r="HA5" s="3"/>
+      <c r="HB5" s="3"/>
+      <c r="HC5" s="3"/>
+      <c r="HD5" s="3"/>
+      <c r="HE5" s="3"/>
+      <c r="HF5" s="3"/>
+      <c r="HG5" s="3"/>
+      <c r="HH5" s="3"/>
+      <c r="HI5" s="3"/>
+      <c r="HJ5" s="3"/>
+      <c r="HK5" s="3"/>
+      <c r="HL5" s="3"/>
+      <c r="HM5" s="3"/>
+      <c r="HN5" s="3"/>
+      <c r="HO5" s="3"/>
+      <c r="HP5" s="3"/>
+      <c r="HQ5" s="3"/>
+      <c r="HR5" s="3"/>
+      <c r="HS5" s="3"/>
+      <c r="HT5" s="3"/>
+      <c r="HU5" s="3"/>
+      <c r="HV5" s="3"/>
+      <c r="HW5" s="3"/>
+      <c r="HX5" s="3"/>
+      <c r="HY5" s="3"/>
+      <c r="HZ5" s="3"/>
+      <c r="IA5" s="3"/>
+      <c r="IB5" s="3"/>
+      <c r="IC5" s="3"/>
+      <c r="ID5" s="3"/>
+      <c r="IE5" s="3"/>
+      <c r="IF5" s="3"/>
+      <c r="IG5" s="3"/>
+      <c r="IH5" s="3"/>
+      <c r="II5" s="3"/>
+      <c r="IJ5" s="3"/>
+      <c r="IK5" s="3"/>
+      <c r="IL5" s="3"/>
+      <c r="IM5" s="3"/>
+      <c r="IN5" s="3"/>
+      <c r="IO5" s="3"/>
+      <c r="IP5" s="3"/>
+      <c r="IQ5" s="3"/>
+      <c r="IR5" s="3"/>
+      <c r="IS5" s="3"/>
+      <c r="IT5" s="3"/>
+      <c r="IU5" s="3"/>
+      <c r="IV5" s="3"/>
+      <c r="IW5" s="3"/>
+      <c r="IX5" s="3"/>
+      <c r="IY5" s="3"/>
+      <c r="IZ5" s="3"/>
+      <c r="JA5" s="3"/>
+      <c r="JB5" s="3"/>
+      <c r="JC5" s="3"/>
+      <c r="JD5" s="3"/>
+      <c r="JE5" s="3"/>
+      <c r="JF5" s="3"/>
+      <c r="JG5" s="3"/>
+      <c r="JH5" s="3"/>
+      <c r="JI5" s="3"/>
+      <c r="JJ5" s="3"/>
+      <c r="JK5" s="3"/>
+      <c r="JL5" s="3"/>
+      <c r="JM5" s="3"/>
+      <c r="JN5" s="3"/>
+      <c r="JO5" s="3"/>
+      <c r="JP5" s="3"/>
+      <c r="JQ5" s="3"/>
+      <c r="JR5" s="3"/>
+      <c r="JS5" s="3"/>
+      <c r="JT5" s="3"/>
+      <c r="JU5" s="3"/>
+      <c r="JV5" s="3"/>
+      <c r="JW5" s="3"/>
+      <c r="JX5" s="3"/>
+      <c r="JY5" s="3"/>
+      <c r="JZ5" s="3"/>
+      <c r="KA5" s="3"/>
+      <c r="KB5" s="3"/>
+      <c r="KC5" s="3"/>
+      <c r="KD5" s="3"/>
+      <c r="KE5" s="3"/>
+      <c r="KF5" s="3"/>
+      <c r="KG5" s="3"/>
+      <c r="KH5" s="3"/>
+      <c r="KI5" s="3"/>
+      <c r="KJ5" s="3"/>
+      <c r="KK5" s="3"/>
+      <c r="KL5" s="3"/>
+      <c r="KM5" s="3"/>
+      <c r="KN5" s="3"/>
+      <c r="KO5" s="3"/>
+      <c r="KP5" s="3"/>
+      <c r="KQ5" s="3"/>
+      <c r="KR5" s="3"/>
+      <c r="KS5" s="3"/>
+      <c r="KT5" s="3"/>
+      <c r="KU5" s="3"/>
+      <c r="KV5" s="3"/>
+      <c r="KW5" s="3"/>
+      <c r="KX5" s="3"/>
+      <c r="KY5" s="3"/>
+      <c r="KZ5" s="3"/>
+      <c r="LA5" s="3"/>
+      <c r="LB5" s="3"/>
+      <c r="LC5" s="3"/>
+      <c r="LD5" s="3"/>
+      <c r="LE5" s="3"/>
+      <c r="LF5" s="3"/>
+      <c r="LG5" s="3"/>
+      <c r="LH5" s="3"/>
+      <c r="LI5" s="3"/>
+      <c r="LJ5" s="3"/>
+      <c r="LK5" s="3"/>
+      <c r="LL5" s="3"/>
+      <c r="LM5" s="3"/>
+      <c r="LN5" s="3"/>
+      <c r="LO5" s="3"/>
+      <c r="LP5" s="3"/>
+      <c r="LQ5" s="3"/>
+      <c r="LR5" s="3"/>
+      <c r="LS5" s="3"/>
+      <c r="LT5" s="3"/>
+      <c r="LU5" s="3"/>
+      <c r="LV5" s="3"/>
+      <c r="LW5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="80" customHeight="1" spans="1:335">
+      <c r="A6" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="I6" s="19"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+      <c r="AO6" s="3"/>
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="3"/>
+      <c r="AR6" s="3"/>
+      <c r="AS6" s="3"/>
+      <c r="AT6" s="3"/>
+      <c r="AU6" s="3"/>
+      <c r="AV6" s="3"/>
+      <c r="AW6" s="3"/>
+      <c r="AX6" s="3"/>
+      <c r="AY6" s="3"/>
+      <c r="AZ6" s="3"/>
+      <c r="BA6" s="3"/>
+      <c r="BB6" s="3"/>
+      <c r="BC6" s="3"/>
+      <c r="BD6" s="3"/>
+      <c r="BE6" s="3"/>
+      <c r="BF6" s="3"/>
+      <c r="BG6" s="3"/>
+      <c r="BH6" s="3"/>
+      <c r="BI6" s="3"/>
+      <c r="BJ6" s="3"/>
+      <c r="BK6" s="3"/>
+      <c r="BL6" s="3"/>
+      <c r="BM6" s="3"/>
+      <c r="BN6" s="3"/>
+      <c r="BO6" s="3"/>
+      <c r="BP6" s="3"/>
+      <c r="BQ6" s="3"/>
+      <c r="BR6" s="3"/>
+      <c r="BS6" s="3"/>
+      <c r="BT6" s="3"/>
+      <c r="BU6" s="3"/>
+      <c r="BV6" s="3"/>
+      <c r="BW6" s="3"/>
+      <c r="BX6" s="3"/>
+      <c r="BY6" s="3"/>
+      <c r="BZ6" s="3"/>
+      <c r="CA6" s="3"/>
+      <c r="CB6" s="3"/>
+      <c r="CC6" s="3"/>
+      <c r="CD6" s="3"/>
+      <c r="CE6" s="3"/>
+      <c r="CF6" s="3"/>
+      <c r="CG6" s="3"/>
+      <c r="CH6" s="3"/>
+      <c r="CI6" s="3"/>
+      <c r="CJ6" s="3"/>
+      <c r="CK6" s="3"/>
+      <c r="CL6" s="3"/>
+      <c r="CM6" s="3"/>
+      <c r="CN6" s="3"/>
+      <c r="CO6" s="3"/>
+      <c r="CP6" s="3"/>
+      <c r="CQ6" s="3"/>
+      <c r="CR6" s="3"/>
+      <c r="CS6" s="3"/>
+      <c r="CT6" s="3"/>
+      <c r="CU6" s="3"/>
+      <c r="CV6" s="3"/>
+      <c r="CW6" s="3"/>
+      <c r="CX6" s="3"/>
+      <c r="CY6" s="3"/>
+      <c r="CZ6" s="3"/>
+      <c r="DA6" s="3"/>
+      <c r="DB6" s="3"/>
+      <c r="DC6" s="3"/>
+      <c r="DD6" s="3"/>
+      <c r="DE6" s="3"/>
+      <c r="DF6" s="3"/>
+      <c r="DG6" s="3"/>
+      <c r="DH6" s="3"/>
+      <c r="DI6" s="3"/>
+      <c r="DJ6" s="3"/>
+      <c r="DK6" s="3"/>
+      <c r="DL6" s="3"/>
+      <c r="DM6" s="3"/>
+      <c r="DN6" s="3"/>
+      <c r="DO6" s="3"/>
+      <c r="DP6" s="3"/>
+      <c r="DQ6" s="3"/>
+      <c r="DR6" s="3"/>
+      <c r="DS6" s="3"/>
+      <c r="DT6" s="3"/>
+      <c r="DU6" s="3"/>
+      <c r="DV6" s="3"/>
+      <c r="DW6" s="3"/>
+      <c r="DX6" s="3"/>
+      <c r="DY6" s="3"/>
+      <c r="DZ6" s="3"/>
+      <c r="EA6" s="3"/>
+      <c r="EB6" s="3"/>
+      <c r="EC6" s="3"/>
+      <c r="ED6" s="3"/>
+      <c r="EE6" s="3"/>
+      <c r="EF6" s="3"/>
+      <c r="EG6" s="3"/>
+      <c r="EH6" s="3"/>
+      <c r="EI6" s="3"/>
+      <c r="EJ6" s="3"/>
+      <c r="EK6" s="3"/>
+      <c r="EL6" s="3"/>
+      <c r="EM6" s="3"/>
+      <c r="EN6" s="3"/>
+      <c r="EO6" s="3"/>
+      <c r="EP6" s="3"/>
+      <c r="EQ6" s="3"/>
+      <c r="ER6" s="3"/>
+      <c r="ES6" s="3"/>
+      <c r="ET6" s="3"/>
+      <c r="EU6" s="3"/>
+      <c r="EV6" s="3"/>
+      <c r="EW6" s="3"/>
+      <c r="EX6" s="3"/>
+      <c r="EY6" s="3"/>
+      <c r="EZ6" s="3"/>
+      <c r="FA6" s="3"/>
+      <c r="FB6" s="3"/>
+      <c r="FC6" s="3"/>
+      <c r="FD6" s="3"/>
+      <c r="FE6" s="3"/>
+      <c r="FF6" s="3"/>
+      <c r="FG6" s="3"/>
+      <c r="FH6" s="3"/>
+      <c r="FI6" s="3"/>
+      <c r="FJ6" s="3"/>
+      <c r="FK6" s="3"/>
+      <c r="FL6" s="3"/>
+      <c r="FM6" s="3"/>
+      <c r="FN6" s="3"/>
+      <c r="FO6" s="3"/>
+      <c r="FP6" s="3"/>
+      <c r="FQ6" s="3"/>
+      <c r="FR6" s="3"/>
+      <c r="FS6" s="3"/>
+      <c r="FT6" s="3"/>
+      <c r="FU6" s="3"/>
+      <c r="FV6" s="3"/>
+      <c r="FW6" s="3"/>
+      <c r="FX6" s="3"/>
+      <c r="FY6" s="3"/>
+      <c r="FZ6" s="3"/>
+      <c r="GA6" s="3"/>
+      <c r="GB6" s="3"/>
+      <c r="GC6" s="3"/>
+      <c r="GD6" s="3"/>
+      <c r="GE6" s="3"/>
+      <c r="GF6" s="3"/>
+      <c r="GG6" s="3"/>
+      <c r="GH6" s="3"/>
+      <c r="GI6" s="3"/>
+      <c r="GJ6" s="3"/>
+      <c r="GK6" s="3"/>
+      <c r="GL6" s="3"/>
+      <c r="GM6" s="3"/>
+      <c r="GN6" s="3"/>
+      <c r="GO6" s="3"/>
+      <c r="GP6" s="3"/>
+      <c r="GQ6" s="3"/>
+      <c r="GR6" s="3"/>
+      <c r="GS6" s="3"/>
+      <c r="GT6" s="3"/>
+      <c r="GU6" s="3"/>
+      <c r="GV6" s="3"/>
+      <c r="GW6" s="3"/>
+      <c r="GX6" s="3"/>
+      <c r="GY6" s="3"/>
+      <c r="GZ6" s="3"/>
+      <c r="HA6" s="3"/>
+      <c r="HB6" s="3"/>
+      <c r="HC6" s="3"/>
+      <c r="HD6" s="3"/>
+      <c r="HE6" s="3"/>
+      <c r="HF6" s="3"/>
+      <c r="HG6" s="3"/>
+      <c r="HH6" s="3"/>
+      <c r="HI6" s="3"/>
+      <c r="HJ6" s="3"/>
+      <c r="HK6" s="3"/>
+      <c r="HL6" s="3"/>
+      <c r="HM6" s="3"/>
+      <c r="HN6" s="3"/>
+      <c r="HO6" s="3"/>
+      <c r="HP6" s="3"/>
+      <c r="HQ6" s="3"/>
+      <c r="HR6" s="3"/>
+      <c r="HS6" s="3"/>
+      <c r="HT6" s="3"/>
+      <c r="HU6" s="3"/>
+      <c r="HV6" s="3"/>
+      <c r="HW6" s="3"/>
+      <c r="HX6" s="3"/>
+      <c r="HY6" s="3"/>
+      <c r="HZ6" s="3"/>
+      <c r="IA6" s="3"/>
+      <c r="IB6" s="3"/>
+      <c r="IC6" s="3"/>
+      <c r="ID6" s="3"/>
+      <c r="IE6" s="3"/>
+      <c r="IF6" s="3"/>
+      <c r="IG6" s="3"/>
+      <c r="IH6" s="3"/>
+      <c r="II6" s="3"/>
+      <c r="IJ6" s="3"/>
+      <c r="IK6" s="3"/>
+      <c r="IL6" s="3"/>
+      <c r="IM6" s="3"/>
+      <c r="IN6" s="3"/>
+      <c r="IO6" s="3"/>
+      <c r="IP6" s="3"/>
+      <c r="IQ6" s="3"/>
+      <c r="IR6" s="3"/>
+      <c r="IS6" s="3"/>
+      <c r="IT6" s="3"/>
+      <c r="IU6" s="3"/>
+      <c r="IV6" s="3"/>
+      <c r="IW6" s="3"/>
+      <c r="IX6" s="3"/>
+      <c r="IY6" s="3"/>
+      <c r="IZ6" s="3"/>
+      <c r="JA6" s="3"/>
+      <c r="JB6" s="3"/>
+      <c r="JC6" s="3"/>
+      <c r="JD6" s="3"/>
+      <c r="JE6" s="3"/>
+      <c r="JF6" s="3"/>
+      <c r="JG6" s="3"/>
+      <c r="JH6" s="3"/>
+      <c r="JI6" s="3"/>
+      <c r="JJ6" s="3"/>
+      <c r="JK6" s="3"/>
+      <c r="JL6" s="3"/>
+      <c r="JM6" s="3"/>
+      <c r="JN6" s="3"/>
+      <c r="JO6" s="3"/>
+      <c r="JP6" s="3"/>
+      <c r="JQ6" s="3"/>
+      <c r="JR6" s="3"/>
+      <c r="JS6" s="3"/>
+      <c r="JT6" s="3"/>
+      <c r="JU6" s="3"/>
+      <c r="JV6" s="3"/>
+      <c r="JW6" s="3"/>
+      <c r="JX6" s="3"/>
+      <c r="JY6" s="3"/>
+      <c r="JZ6" s="3"/>
+      <c r="KA6" s="3"/>
+      <c r="KB6" s="3"/>
+      <c r="KC6" s="3"/>
+      <c r="KD6" s="3"/>
+      <c r="KE6" s="3"/>
+      <c r="KF6" s="3"/>
+      <c r="KG6" s="3"/>
+      <c r="KH6" s="3"/>
+      <c r="KI6" s="3"/>
+      <c r="KJ6" s="3"/>
+      <c r="KK6" s="3"/>
+      <c r="KL6" s="3"/>
+      <c r="KM6" s="3"/>
+      <c r="KN6" s="3"/>
+      <c r="KO6" s="3"/>
+      <c r="KP6" s="3"/>
+      <c r="KQ6" s="3"/>
+      <c r="KR6" s="3"/>
+      <c r="KS6" s="3"/>
+      <c r="KT6" s="3"/>
+      <c r="KU6" s="3"/>
+      <c r="KV6" s="3"/>
+      <c r="KW6" s="3"/>
+      <c r="KX6" s="3"/>
+      <c r="KY6" s="3"/>
+      <c r="KZ6" s="3"/>
+      <c r="LA6" s="3"/>
+      <c r="LB6" s="3"/>
+      <c r="LC6" s="3"/>
+      <c r="LD6" s="3"/>
+      <c r="LE6" s="3"/>
+      <c r="LF6" s="3"/>
+      <c r="LG6" s="3"/>
+      <c r="LH6" s="3"/>
+      <c r="LI6" s="3"/>
+      <c r="LJ6" s="3"/>
+      <c r="LK6" s="3"/>
+      <c r="LL6" s="3"/>
+      <c r="LM6" s="3"/>
+      <c r="LN6" s="3"/>
+      <c r="LO6" s="3"/>
+      <c r="LP6" s="3"/>
+      <c r="LQ6" s="3"/>
+      <c r="LR6" s="3"/>
+      <c r="LS6" s="3"/>
+      <c r="LT6" s="3"/>
+      <c r="LU6" s="3"/>
+      <c r="LV6" s="3"/>
+      <c r="LW6" s="3"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="80" customHeight="1" spans="1:335">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+      <c r="AO7" s="3"/>
+      <c r="AP7" s="3"/>
+      <c r="AQ7" s="3"/>
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="3"/>
+      <c r="AT7" s="3"/>
+      <c r="AU7" s="3"/>
+      <c r="AV7" s="3"/>
+      <c r="AW7" s="3"/>
+      <c r="AX7" s="3"/>
+      <c r="AY7" s="3"/>
+      <c r="AZ7" s="3"/>
+      <c r="BA7" s="3"/>
+      <c r="BB7" s="3"/>
+      <c r="BC7" s="3"/>
+      <c r="BD7" s="3"/>
+      <c r="BE7" s="3"/>
+      <c r="BF7" s="3"/>
+      <c r="BG7" s="3"/>
+      <c r="BH7" s="3"/>
+      <c r="BI7" s="3"/>
+      <c r="BJ7" s="3"/>
+      <c r="BK7" s="3"/>
+      <c r="BL7" s="3"/>
+      <c r="BM7" s="3"/>
+      <c r="BN7" s="3"/>
+      <c r="BO7" s="3"/>
+      <c r="BP7" s="3"/>
+      <c r="BQ7" s="3"/>
+      <c r="BR7" s="3"/>
+      <c r="BS7" s="3"/>
+      <c r="BT7" s="3"/>
+      <c r="BU7" s="3"/>
+      <c r="BV7" s="3"/>
+      <c r="BW7" s="3"/>
+      <c r="BX7" s="3"/>
+      <c r="BY7" s="3"/>
+      <c r="BZ7" s="3"/>
+      <c r="CA7" s="3"/>
+      <c r="CB7" s="3"/>
+      <c r="CC7" s="3"/>
+      <c r="CD7" s="3"/>
+      <c r="CE7" s="3"/>
+      <c r="CF7" s="3"/>
+      <c r="CG7" s="3"/>
+      <c r="CH7" s="3"/>
+      <c r="CI7" s="3"/>
+      <c r="CJ7" s="3"/>
+      <c r="CK7" s="3"/>
+      <c r="CL7" s="3"/>
+      <c r="CM7" s="3"/>
+      <c r="CN7" s="3"/>
+      <c r="CO7" s="3"/>
+      <c r="CP7" s="3"/>
+      <c r="CQ7" s="3"/>
+      <c r="CR7" s="3"/>
+      <c r="CS7" s="3"/>
+      <c r="CT7" s="3"/>
+      <c r="CU7" s="3"/>
+      <c r="CV7" s="3"/>
+      <c r="CW7" s="3"/>
+      <c r="CX7" s="3"/>
+      <c r="CY7" s="3"/>
+      <c r="CZ7" s="3"/>
+      <c r="DA7" s="3"/>
+      <c r="DB7" s="3"/>
+      <c r="DC7" s="3"/>
+      <c r="DD7" s="3"/>
+      <c r="DE7" s="3"/>
+      <c r="DF7" s="3"/>
+      <c r="DG7" s="3"/>
+      <c r="DH7" s="3"/>
+      <c r="DI7" s="3"/>
+      <c r="DJ7" s="3"/>
+      <c r="DK7" s="3"/>
+      <c r="DL7" s="3"/>
+      <c r="DM7" s="3"/>
+      <c r="DN7" s="3"/>
+      <c r="DO7" s="3"/>
+      <c r="DP7" s="3"/>
+      <c r="DQ7" s="3"/>
+      <c r="DR7" s="3"/>
+      <c r="DS7" s="3"/>
+      <c r="DT7" s="3"/>
+      <c r="DU7" s="3"/>
+      <c r="DV7" s="3"/>
+      <c r="DW7" s="3"/>
+      <c r="DX7" s="3"/>
+      <c r="DY7" s="3"/>
+      <c r="DZ7" s="3"/>
+      <c r="EA7" s="3"/>
+      <c r="EB7" s="3"/>
+      <c r="EC7" s="3"/>
+      <c r="ED7" s="3"/>
+      <c r="EE7" s="3"/>
+      <c r="EF7" s="3"/>
+      <c r="EG7" s="3"/>
+      <c r="EH7" s="3"/>
+      <c r="EI7" s="3"/>
+      <c r="EJ7" s="3"/>
+      <c r="EK7" s="3"/>
+      <c r="EL7" s="3"/>
+      <c r="EM7" s="3"/>
+      <c r="EN7" s="3"/>
+      <c r="EO7" s="3"/>
+      <c r="EP7" s="3"/>
+      <c r="EQ7" s="3"/>
+      <c r="ER7" s="3"/>
+      <c r="ES7" s="3"/>
+      <c r="ET7" s="3"/>
+      <c r="EU7" s="3"/>
+      <c r="EV7" s="3"/>
+      <c r="EW7" s="3"/>
+      <c r="EX7" s="3"/>
+      <c r="EY7" s="3"/>
+      <c r="EZ7" s="3"/>
+      <c r="FA7" s="3"/>
+      <c r="FB7" s="3"/>
+      <c r="FC7" s="3"/>
+      <c r="FD7" s="3"/>
+      <c r="FE7" s="3"/>
+      <c r="FF7" s="3"/>
+      <c r="FG7" s="3"/>
+      <c r="FH7" s="3"/>
+      <c r="FI7" s="3"/>
+      <c r="FJ7" s="3"/>
+      <c r="FK7" s="3"/>
+      <c r="FL7" s="3"/>
+      <c r="FM7" s="3"/>
+      <c r="FN7" s="3"/>
+      <c r="FO7" s="3"/>
+      <c r="FP7" s="3"/>
+      <c r="FQ7" s="3"/>
+      <c r="FR7" s="3"/>
+      <c r="FS7" s="3"/>
+      <c r="FT7" s="3"/>
+      <c r="FU7" s="3"/>
+      <c r="FV7" s="3"/>
+      <c r="FW7" s="3"/>
+      <c r="FX7" s="3"/>
+      <c r="FY7" s="3"/>
+      <c r="FZ7" s="3"/>
+      <c r="GA7" s="3"/>
+      <c r="GB7" s="3"/>
+      <c r="GC7" s="3"/>
+      <c r="GD7" s="3"/>
+      <c r="GE7" s="3"/>
+      <c r="GF7" s="3"/>
+      <c r="GG7" s="3"/>
+      <c r="GH7" s="3"/>
+      <c r="GI7" s="3"/>
+      <c r="GJ7" s="3"/>
+      <c r="GK7" s="3"/>
+      <c r="GL7" s="3"/>
+      <c r="GM7" s="3"/>
+      <c r="GN7" s="3"/>
+      <c r="GO7" s="3"/>
+      <c r="GP7" s="3"/>
+      <c r="GQ7" s="3"/>
+      <c r="GR7" s="3"/>
+      <c r="GS7" s="3"/>
+      <c r="GT7" s="3"/>
+      <c r="GU7" s="3"/>
+      <c r="GV7" s="3"/>
+      <c r="GW7" s="3"/>
+      <c r="GX7" s="3"/>
+      <c r="GY7" s="3"/>
+      <c r="GZ7" s="3"/>
+      <c r="HA7" s="3"/>
+      <c r="HB7" s="3"/>
+      <c r="HC7" s="3"/>
+      <c r="HD7" s="3"/>
+      <c r="HE7" s="3"/>
+      <c r="HF7" s="3"/>
+      <c r="HG7" s="3"/>
+      <c r="HH7" s="3"/>
+      <c r="HI7" s="3"/>
+      <c r="HJ7" s="3"/>
+      <c r="HK7" s="3"/>
+      <c r="HL7" s="3"/>
+      <c r="HM7" s="3"/>
+      <c r="HN7" s="3"/>
+      <c r="HO7" s="3"/>
+      <c r="HP7" s="3"/>
+      <c r="HQ7" s="3"/>
+      <c r="HR7" s="3"/>
+      <c r="HS7" s="3"/>
+      <c r="HT7" s="3"/>
+      <c r="HU7" s="3"/>
+      <c r="HV7" s="3"/>
+      <c r="HW7" s="3"/>
+      <c r="HX7" s="3"/>
+      <c r="HY7" s="3"/>
+      <c r="HZ7" s="3"/>
+      <c r="IA7" s="3"/>
+      <c r="IB7" s="3"/>
+      <c r="IC7" s="3"/>
+      <c r="ID7" s="3"/>
+      <c r="IE7" s="3"/>
+      <c r="IF7" s="3"/>
+      <c r="IG7" s="3"/>
+      <c r="IH7" s="3"/>
+      <c r="II7" s="3"/>
+      <c r="IJ7" s="3"/>
+      <c r="IK7" s="3"/>
+      <c r="IL7" s="3"/>
+      <c r="IM7" s="3"/>
+      <c r="IN7" s="3"/>
+      <c r="IO7" s="3"/>
+      <c r="IP7" s="3"/>
+      <c r="IQ7" s="3"/>
+      <c r="IR7" s="3"/>
+      <c r="IS7" s="3"/>
+      <c r="IT7" s="3"/>
+      <c r="IU7" s="3"/>
+      <c r="IV7" s="3"/>
+      <c r="IW7" s="3"/>
+      <c r="IX7" s="3"/>
+      <c r="IY7" s="3"/>
+      <c r="IZ7" s="3"/>
+      <c r="JA7" s="3"/>
+      <c r="JB7" s="3"/>
+      <c r="JC7" s="3"/>
+      <c r="JD7" s="3"/>
+      <c r="JE7" s="3"/>
+      <c r="JF7" s="3"/>
+      <c r="JG7" s="3"/>
+      <c r="JH7" s="3"/>
+      <c r="JI7" s="3"/>
+      <c r="JJ7" s="3"/>
+      <c r="JK7" s="3"/>
+      <c r="JL7" s="3"/>
+      <c r="JM7" s="3"/>
+      <c r="JN7" s="3"/>
+      <c r="JO7" s="3"/>
+      <c r="JP7" s="3"/>
+      <c r="JQ7" s="3"/>
+      <c r="JR7" s="3"/>
+      <c r="JS7" s="3"/>
+      <c r="JT7" s="3"/>
+      <c r="JU7" s="3"/>
+      <c r="JV7" s="3"/>
+      <c r="JW7" s="3"/>
+      <c r="JX7" s="3"/>
+      <c r="JY7" s="3"/>
+      <c r="JZ7" s="3"/>
+      <c r="KA7" s="3"/>
+      <c r="KB7" s="3"/>
+      <c r="KC7" s="3"/>
+      <c r="KD7" s="3"/>
+      <c r="KE7" s="3"/>
+      <c r="KF7" s="3"/>
+      <c r="KG7" s="3"/>
+      <c r="KH7" s="3"/>
+      <c r="KI7" s="3"/>
+      <c r="KJ7" s="3"/>
+      <c r="KK7" s="3"/>
+      <c r="KL7" s="3"/>
+      <c r="KM7" s="3"/>
+      <c r="KN7" s="3"/>
+      <c r="KO7" s="3"/>
+      <c r="KP7" s="3"/>
+      <c r="KQ7" s="3"/>
+      <c r="KR7" s="3"/>
+      <c r="KS7" s="3"/>
+      <c r="KT7" s="3"/>
+      <c r="KU7" s="3"/>
+      <c r="KV7" s="3"/>
+      <c r="KW7" s="3"/>
+      <c r="KX7" s="3"/>
+      <c r="KY7" s="3"/>
+      <c r="KZ7" s="3"/>
+      <c r="LA7" s="3"/>
+      <c r="LB7" s="3"/>
+      <c r="LC7" s="3"/>
+      <c r="LD7" s="3"/>
+      <c r="LE7" s="3"/>
+      <c r="LF7" s="3"/>
+      <c r="LG7" s="3"/>
+      <c r="LH7" s="3"/>
+      <c r="LI7" s="3"/>
+      <c r="LJ7" s="3"/>
+      <c r="LK7" s="3"/>
+      <c r="LL7" s="3"/>
+      <c r="LM7" s="3"/>
+      <c r="LN7" s="3"/>
+      <c r="LO7" s="3"/>
+      <c r="LP7" s="3"/>
+      <c r="LQ7" s="3"/>
+      <c r="LR7" s="3"/>
+      <c r="LS7" s="3"/>
+      <c r="LT7" s="3"/>
+      <c r="LU7" s="3"/>
+      <c r="LV7" s="3"/>
+      <c r="LW7" s="3"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="80" customHeight="1" spans="1:335">
+      <c r="A8" s="24"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3"/>
+      <c r="AV8" s="3"/>
+      <c r="AW8" s="3"/>
+      <c r="AX8" s="3"/>
+      <c r="AY8" s="3"/>
+      <c r="AZ8" s="3"/>
+      <c r="BA8" s="3"/>
+      <c r="BB8" s="3"/>
+      <c r="BC8" s="3"/>
+      <c r="BD8" s="3"/>
+      <c r="BE8" s="3"/>
+      <c r="BF8" s="3"/>
+      <c r="BG8" s="3"/>
+      <c r="BH8" s="3"/>
+      <c r="BI8" s="3"/>
+      <c r="BJ8" s="3"/>
+      <c r="BK8" s="3"/>
+      <c r="BL8" s="3"/>
+      <c r="BM8" s="3"/>
+      <c r="BN8" s="3"/>
+      <c r="BO8" s="3"/>
+      <c r="BP8" s="3"/>
+      <c r="BQ8" s="3"/>
+      <c r="BR8" s="3"/>
+      <c r="BS8" s="3"/>
+      <c r="BT8" s="3"/>
+      <c r="BU8" s="3"/>
+      <c r="BV8" s="3"/>
+      <c r="BW8" s="3"/>
+      <c r="BX8" s="3"/>
+      <c r="BY8" s="3"/>
+      <c r="BZ8" s="3"/>
+      <c r="CA8" s="3"/>
+      <c r="CB8" s="3"/>
+      <c r="CC8" s="3"/>
+      <c r="CD8" s="3"/>
+      <c r="CE8" s="3"/>
+      <c r="CF8" s="3"/>
+      <c r="CG8" s="3"/>
+      <c r="CH8" s="3"/>
+      <c r="CI8" s="3"/>
+      <c r="CJ8" s="3"/>
+      <c r="CK8" s="3"/>
+      <c r="CL8" s="3"/>
+      <c r="CM8" s="3"/>
+      <c r="CN8" s="3"/>
+      <c r="CO8" s="3"/>
+      <c r="CP8" s="3"/>
+      <c r="CQ8" s="3"/>
+      <c r="CR8" s="3"/>
+      <c r="CS8" s="3"/>
+      <c r="CT8" s="3"/>
+      <c r="CU8" s="3"/>
+      <c r="CV8" s="3"/>
+      <c r="CW8" s="3"/>
+      <c r="CX8" s="3"/>
+      <c r="CY8" s="3"/>
+      <c r="CZ8" s="3"/>
+      <c r="DA8" s="3"/>
+      <c r="DB8" s="3"/>
+      <c r="DC8" s="3"/>
+      <c r="DD8" s="3"/>
+      <c r="DE8" s="3"/>
+      <c r="DF8" s="3"/>
+      <c r="DG8" s="3"/>
+      <c r="DH8" s="3"/>
+      <c r="DI8" s="3"/>
+      <c r="DJ8" s="3"/>
+      <c r="DK8" s="3"/>
+      <c r="DL8" s="3"/>
+      <c r="DM8" s="3"/>
+      <c r="DN8" s="3"/>
+      <c r="DO8" s="3"/>
+      <c r="DP8" s="3"/>
+      <c r="DQ8" s="3"/>
+      <c r="DR8" s="3"/>
+      <c r="DS8" s="3"/>
+      <c r="DT8" s="3"/>
+      <c r="DU8" s="3"/>
+      <c r="DV8" s="3"/>
+      <c r="DW8" s="3"/>
+      <c r="DX8" s="3"/>
+      <c r="DY8" s="3"/>
+      <c r="DZ8" s="3"/>
+      <c r="EA8" s="3"/>
+      <c r="EB8" s="3"/>
+      <c r="EC8" s="3"/>
+      <c r="ED8" s="3"/>
+      <c r="EE8" s="3"/>
+      <c r="EF8" s="3"/>
+      <c r="EG8" s="3"/>
+      <c r="EH8" s="3"/>
+      <c r="EI8" s="3"/>
+      <c r="EJ8" s="3"/>
+      <c r="EK8" s="3"/>
+      <c r="EL8" s="3"/>
+      <c r="EM8" s="3"/>
+      <c r="EN8" s="3"/>
+      <c r="EO8" s="3"/>
+      <c r="EP8" s="3"/>
+      <c r="EQ8" s="3"/>
+      <c r="ER8" s="3"/>
+      <c r="ES8" s="3"/>
+      <c r="ET8" s="3"/>
+      <c r="EU8" s="3"/>
+      <c r="EV8" s="3"/>
+      <c r="EW8" s="3"/>
+      <c r="EX8" s="3"/>
+      <c r="EY8" s="3"/>
+      <c r="EZ8" s="3"/>
+      <c r="FA8" s="3"/>
+      <c r="FB8" s="3"/>
+      <c r="FC8" s="3"/>
+      <c r="FD8" s="3"/>
+      <c r="FE8" s="3"/>
+      <c r="FF8" s="3"/>
+      <c r="FG8" s="3"/>
+      <c r="FH8" s="3"/>
+      <c r="FI8" s="3"/>
+      <c r="FJ8" s="3"/>
+      <c r="FK8" s="3"/>
+      <c r="FL8" s="3"/>
+      <c r="FM8" s="3"/>
+      <c r="FN8" s="3"/>
+      <c r="FO8" s="3"/>
+      <c r="FP8" s="3"/>
+      <c r="FQ8" s="3"/>
+      <c r="FR8" s="3"/>
+      <c r="FS8" s="3"/>
+      <c r="FT8" s="3"/>
+      <c r="FU8" s="3"/>
+      <c r="FV8" s="3"/>
+      <c r="FW8" s="3"/>
+      <c r="FX8" s="3"/>
+      <c r="FY8" s="3"/>
+      <c r="FZ8" s="3"/>
+      <c r="GA8" s="3"/>
+      <c r="GB8" s="3"/>
+      <c r="GC8" s="3"/>
+      <c r="GD8" s="3"/>
+      <c r="GE8" s="3"/>
+      <c r="GF8" s="3"/>
+      <c r="GG8" s="3"/>
+      <c r="GH8" s="3"/>
+      <c r="GI8" s="3"/>
+      <c r="GJ8" s="3"/>
+      <c r="GK8" s="3"/>
+      <c r="GL8" s="3"/>
+      <c r="GM8" s="3"/>
+      <c r="GN8" s="3"/>
+      <c r="GO8" s="3"/>
+      <c r="GP8" s="3"/>
+      <c r="GQ8" s="3"/>
+      <c r="GR8" s="3"/>
+      <c r="GS8" s="3"/>
+      <c r="GT8" s="3"/>
+      <c r="GU8" s="3"/>
+      <c r="GV8" s="3"/>
+      <c r="GW8" s="3"/>
+      <c r="GX8" s="3"/>
+      <c r="GY8" s="3"/>
+      <c r="GZ8" s="3"/>
+      <c r="HA8" s="3"/>
+      <c r="HB8" s="3"/>
+      <c r="HC8" s="3"/>
+      <c r="HD8" s="3"/>
+      <c r="HE8" s="3"/>
+      <c r="HF8" s="3"/>
+      <c r="HG8" s="3"/>
+      <c r="HH8" s="3"/>
+      <c r="HI8" s="3"/>
+      <c r="HJ8" s="3"/>
+      <c r="HK8" s="3"/>
+      <c r="HL8" s="3"/>
+      <c r="HM8" s="3"/>
+      <c r="HN8" s="3"/>
+      <c r="HO8" s="3"/>
+      <c r="HP8" s="3"/>
+      <c r="HQ8" s="3"/>
+      <c r="HR8" s="3"/>
+      <c r="HS8" s="3"/>
+      <c r="HT8" s="3"/>
+      <c r="HU8" s="3"/>
+      <c r="HV8" s="3"/>
+      <c r="HW8" s="3"/>
+      <c r="HX8" s="3"/>
+      <c r="HY8" s="3"/>
+      <c r="HZ8" s="3"/>
+      <c r="IA8" s="3"/>
+      <c r="IB8" s="3"/>
+      <c r="IC8" s="3"/>
+      <c r="ID8" s="3"/>
+      <c r="IE8" s="3"/>
+      <c r="IF8" s="3"/>
+      <c r="IG8" s="3"/>
+      <c r="IH8" s="3"/>
+      <c r="II8" s="3"/>
+      <c r="IJ8" s="3"/>
+      <c r="IK8" s="3"/>
+      <c r="IL8" s="3"/>
+      <c r="IM8" s="3"/>
+      <c r="IN8" s="3"/>
+      <c r="IO8" s="3"/>
+      <c r="IP8" s="3"/>
+      <c r="IQ8" s="3"/>
+      <c r="IR8" s="3"/>
+      <c r="IS8" s="3"/>
+      <c r="IT8" s="3"/>
+      <c r="IU8" s="3"/>
+      <c r="IV8" s="3"/>
+      <c r="IW8" s="3"/>
+      <c r="IX8" s="3"/>
+      <c r="IY8" s="3"/>
+      <c r="IZ8" s="3"/>
+      <c r="JA8" s="3"/>
+      <c r="JB8" s="3"/>
+      <c r="JC8" s="3"/>
+      <c r="JD8" s="3"/>
+      <c r="JE8" s="3"/>
+      <c r="JF8" s="3"/>
+      <c r="JG8" s="3"/>
+      <c r="JH8" s="3"/>
+      <c r="JI8" s="3"/>
+      <c r="JJ8" s="3"/>
+      <c r="JK8" s="3"/>
+      <c r="JL8" s="3"/>
+      <c r="JM8" s="3"/>
+      <c r="JN8" s="3"/>
+      <c r="JO8" s="3"/>
+      <c r="JP8" s="3"/>
+      <c r="JQ8" s="3"/>
+      <c r="JR8" s="3"/>
+      <c r="JS8" s="3"/>
+      <c r="JT8" s="3"/>
+      <c r="JU8" s="3"/>
+      <c r="JV8" s="3"/>
+      <c r="JW8" s="3"/>
+      <c r="JX8" s="3"/>
+      <c r="JY8" s="3"/>
+      <c r="JZ8" s="3"/>
+      <c r="KA8" s="3"/>
+      <c r="KB8" s="3"/>
+      <c r="KC8" s="3"/>
+      <c r="KD8" s="3"/>
+      <c r="KE8" s="3"/>
+      <c r="KF8" s="3"/>
+      <c r="KG8" s="3"/>
+      <c r="KH8" s="3"/>
+      <c r="KI8" s="3"/>
+      <c r="KJ8" s="3"/>
+      <c r="KK8" s="3"/>
+      <c r="KL8" s="3"/>
+      <c r="KM8" s="3"/>
+      <c r="KN8" s="3"/>
+      <c r="KO8" s="3"/>
+      <c r="KP8" s="3"/>
+      <c r="KQ8" s="3"/>
+      <c r="KR8" s="3"/>
+      <c r="KS8" s="3"/>
+      <c r="KT8" s="3"/>
+      <c r="KU8" s="3"/>
+      <c r="KV8" s="3"/>
+      <c r="KW8" s="3"/>
+      <c r="KX8" s="3"/>
+      <c r="KY8" s="3"/>
+      <c r="KZ8" s="3"/>
+      <c r="LA8" s="3"/>
+      <c r="LB8" s="3"/>
+      <c r="LC8" s="3"/>
+      <c r="LD8" s="3"/>
+      <c r="LE8" s="3"/>
+      <c r="LF8" s="3"/>
+      <c r="LG8" s="3"/>
+      <c r="LH8" s="3"/>
+      <c r="LI8" s="3"/>
+      <c r="LJ8" s="3"/>
+      <c r="LK8" s="3"/>
+      <c r="LL8" s="3"/>
+      <c r="LM8" s="3"/>
+      <c r="LN8" s="3"/>
+      <c r="LO8" s="3"/>
+      <c r="LP8" s="3"/>
+      <c r="LQ8" s="3"/>
+      <c r="LR8" s="3"/>
+      <c r="LS8" s="3"/>
+      <c r="LT8" s="3"/>
+      <c r="LU8" s="3"/>
+      <c r="LV8" s="3"/>
+      <c r="LW8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="158.4" spans="1:10">
+      <c r="A9" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="31"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:10">
+      <c r="A10" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="31"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="144" spans="1:10">
+      <c r="A11" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="31"/>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="350" customHeight="1" spans="1:10">
+      <c r="A12" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="I12" s="13"/>
+      <c r="J12" s="31"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:10">
+      <c r="A13" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="I13" s="13"/>
+      <c r="J13" s="31"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:10">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="31"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:10">
+      <c r="A15" s="31"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="31"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:I7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A12" location="'3.1. API_DB_8'!A1" display="API_DB_8"/>
+    <hyperlink ref="A11" location="'3.2. API_DB_7'!A1" display="API_DB_7"/>
+    <hyperlink ref="A3" location="'3.3. API_DB_1'!A1" display="API_DB_1"/>
+    <hyperlink ref="A4" location="'3.4. API_DB_2'!A1" display="API_DB_2"/>
+    <hyperlink ref="A5" location="'3.5. API_DB_3'!A1" display="API_DB_3"/>
+    <hyperlink ref="A6:A8" location="'3.6. API_DB_4'!A1" display="API_DB_4"/>
+    <hyperlink ref="A9" location="'3.7. API_DB_5'!A1" display="API_DB_5"/>
+    <hyperlink ref="A10" location="'3.8. API_DB_6'!A1" display="API_DB_6"/>
+    <hyperlink ref="A13" location="'3.9. API_DB_15'!A1" display="API_DB_15"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>